--- a/output/pdf_financials_xlsx/GPO.xlsx
+++ b/output/pdf_financials_xlsx/GPO.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.598995</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.598995</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.072093</v>
       </c>
     </row>
     <row r="93">
@@ -3017,7 +3017,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>1.598995</v>
       </c>

--- a/output/pdf_financials_xlsx/GPO.xlsx
+++ b/output/pdf_financials_xlsx/GPO.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.097897</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.051706</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00739</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.217188</v>
+        <v>-1.315085</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.18823</v>
+        <v>-1.239936</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.759958</v>
+        <v>0.752568</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.217188</v>
+        <v>-1.315085</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.18823</v>
+        <v>-1.239936</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.759958</v>
+        <v>0.752568</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.102325</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.803182</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.812494</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.38711</v>
+        <v>2.489435</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.466252</v>
+        <v>1.269434</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2.000488</v>
+        <v>2.812982</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.102325</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.803182</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.812494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">

--- a/output/pdf_financials_xlsx/GPO.xlsx
+++ b/output/pdf_financials_xlsx/GPO.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.257638</v>
+        <v>0.40715</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.206428</v>
+        <v>0.309414</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.224348</v>
+        <v>0.337329</v>
       </c>
     </row>
     <row r="8">
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.021842</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.6002</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -3457,7 +3457,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -3781,7 +3785,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>-0.021842</v>
       </c>
@@ -3938,7 +3946,11 @@
           <t>Director fees 8 $</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.052983</v>
       </c>
@@ -4054,7 +4066,11 @@
           <t>Office expense</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>0.096529</v>
       </c>
